--- a/InputData/io-model/BEbIC/BAU Employment by ISIC Code.xlsx
+++ b/InputData/io-model/BEbIC/BAU Employment by ISIC Code.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t xml:space="preserve">BEbIC - BAU Employment by ISIC Code</t>
   </si>
@@ -40,19 +40,40 @@
     <t xml:space="preserve">fallback (see 32_employment.R):</t>
   </si>
   <si>
-    <t xml:space="preserve">  Tier 1 (Path A, default): stateior's</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  getStateEmploymentbyBEASummary(datasource='Flowsa') - 51 states x 71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BEA Summary employment sourced from EPA's flowsa Data Commons (BLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  QCEW gap-filled at BEA Summary level), aggregated to 42 ISIC via the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  canonical crosswalk.</t>
+    <t xml:space="preserve">  Tier 1 (Path A, default): EPA flowsa BLS-QCEW state employment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (6-digit NAICS), mapped NAICS -&gt; BEA Summary with deduplicated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (NAICS, Summary) pairs - NOT stateior's mapper, whose retained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BEA-Detail column multiple-counts many-to-many sectors (construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ~6.4x; fixed 2026-08-22) - then aggregated to 42 ISIC via the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  canonical crosswalk with this state's override weights.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BASIS: QCEW covered payroll, NO national adjustment (decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2026-08-22). Public-sector staff sit under their activity (schools -&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  education, not government); proprietors and most farm/household</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  labor are absent. Known gaps vs the eps-us national BEbIC are logged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  as FYI lines on every build (construction ~x0.85, education ~x3.3,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  government ~x0.35).</t>
   </si>
   <si>
     <t xml:space="preserve">  Tier 2 (Path B): national employment by ISIC x this state's share of</t>
@@ -817,102 +838,102 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -937,52 +958,52 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55">
@@ -992,232 +1013,232 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>1</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>61</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>1</v>
+        <v>63</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102">
@@ -1227,12 +1248,47 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>76</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1248,261 +1304,261 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="J1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="K1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="N1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="O1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="P1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="Q1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="R1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="S1" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="T1" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="U1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="V1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="W1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="X1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="Y1" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Z1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AA1" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="AB1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="AC1" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="AD1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="AE1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="AF1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="AG1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="AH1" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AI1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="AJ1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="AK1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="AL1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="AM1" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="AN1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="AO1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="AP1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="AQ1" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B2" t="n">
-        <v>20088.39254</v>
+        <v>4180.19164</v>
       </c>
       <c r="C2" t="n">
-        <v>6538.40372</v>
+        <v>1821.01161</v>
       </c>
       <c r="D2" t="n">
-        <v>4107.62679</v>
+        <v>2766.15202</v>
       </c>
       <c r="E2" t="n">
-        <v>53.29028</v>
+        <v>276.43073</v>
       </c>
       <c r="F2" t="n">
-        <v>22767.72023</v>
+        <v>16632.97468</v>
       </c>
       <c r="G2" t="n">
-        <v>4909.29186</v>
+        <v>5469.84844</v>
       </c>
       <c r="H2" t="n">
-        <v>325.40552</v>
+        <v>743.00673</v>
       </c>
       <c r="I2" t="n">
-        <v>2028.36461</v>
+        <v>1970.57575</v>
       </c>
       <c r="J2" t="n">
-        <v>452.11738</v>
+        <v>962.70227</v>
       </c>
       <c r="K2" t="n">
-        <v>182.3596</v>
+        <v>261.44695</v>
       </c>
       <c r="L2" t="n">
-        <v>227.62578</v>
+        <v>369.84098</v>
       </c>
       <c r="M2" t="n">
-        <v>40.16925</v>
+        <v>65.26605</v>
       </c>
       <c r="N2" t="n">
-        <v>1010.65521</v>
+        <v>1467.76025</v>
       </c>
       <c r="O2" t="n">
-        <v>931.26569</v>
+        <v>341.29296</v>
       </c>
       <c r="P2" t="n">
-        <v>931.26569</v>
+        <v>1023.87887</v>
       </c>
       <c r="Q2" t="n">
-        <v>93.90062</v>
+        <v>75.78272</v>
       </c>
       <c r="R2" t="n">
-        <v>992.79329</v>
+        <v>152.06914</v>
       </c>
       <c r="S2" t="n">
-        <v>1544.24083</v>
+        <v>2335.64318</v>
       </c>
       <c r="T2" t="n">
-        <v>584.17526</v>
+        <v>1506.88613</v>
       </c>
       <c r="U2" t="n">
-        <v>56.02819</v>
+        <v>126.47754</v>
       </c>
       <c r="V2" t="n">
-        <v>9956.82494</v>
+        <v>5866.73632</v>
       </c>
       <c r="W2" t="n">
-        <v>1080.56987</v>
+        <v>1695.95606</v>
       </c>
       <c r="X2" t="n">
-        <v>539.10253</v>
+        <v>710.52132</v>
       </c>
       <c r="Y2" t="n">
-        <v>775.42836</v>
+        <v>1319.32828</v>
       </c>
       <c r="Z2" t="n">
-        <v>2494.09115</v>
+        <v>2880.77136</v>
       </c>
       <c r="AA2" t="n">
-        <v>1221.15789</v>
+        <v>2241.59041</v>
       </c>
       <c r="AB2" t="n">
-        <v>1298.38811</v>
+        <v>1051.40947</v>
       </c>
       <c r="AC2" t="n">
-        <v>204482.52181</v>
+        <v>27902.5526</v>
       </c>
       <c r="AD2" t="n">
-        <v>69339.28637</v>
+        <v>69655.35707</v>
       </c>
       <c r="AE2" t="n">
-        <v>24370.30437</v>
+        <v>16502.45989</v>
       </c>
       <c r="AF2" t="n">
-        <v>31947.84342</v>
+        <v>34410.27944</v>
       </c>
       <c r="AG2" t="n">
-        <v>2282.96721</v>
+        <v>3597.45256</v>
       </c>
       <c r="AH2" t="n">
-        <v>1095.61954</v>
+        <v>2081.79268</v>
       </c>
       <c r="AI2" t="n">
-        <v>1836.49072</v>
+        <v>4201.37905</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11386.9306</v>
+        <v>17771.48259</v>
       </c>
       <c r="AK2" t="n">
-        <v>4030.70561</v>
+        <v>3701.92946</v>
       </c>
       <c r="AL2" t="n">
-        <v>28051.67315</v>
+        <v>31613.13642</v>
       </c>
       <c r="AM2" t="n">
-        <v>47260.42456</v>
+        <v>24575.51453</v>
       </c>
       <c r="AN2" t="n">
-        <v>9249.12596</v>
+        <v>34935.55934</v>
       </c>
       <c r="AO2" t="n">
-        <v>66635.55946</v>
+        <v>68328.10658</v>
       </c>
       <c r="AP2" t="n">
-        <v>13381.50561</v>
+        <v>22341.24099</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
